--- a/docs/files/exports/overview-application-pricing-quick-guide.xlsx
+++ b/docs/files/exports/overview-application-pricing-quick-guide.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1,158 words</t>
+          <t>1,118 words</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/docs/files/exports/overview-application-pricing-quick-guide.xlsx
+++ b/docs/files/exports/overview-application-pricing-quick-guide.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1,118 words</t>
+          <t>1,226 words</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>📱 Application Pricing — Quick Reference Guide Condensed version for quick sharing and presentations 🎯 What This Module Does A complete toolkit for pricing mobile app projects (iOS, Android, Cross-Platform). Covers discov...</t>
+          <t>📱 Application Pricing — Quick Reference Guide Condensed version for quick sharing and presentations 🎯 What This Module Does + Add to Scope A complete toolkit for pricing mobile app projects (iOS, Android, Cross-Platform)...</t>
         </is>
       </c>
     </row>
